--- a/artfynd/A 19546-2026 artfynd.xlsx
+++ b/artfynd/A 19546-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108923053</v>
+        <v>133653949</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gruvdammen, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628428.4233511501</v>
+        <v>628483</v>
       </c>
       <c r="R2" t="n">
-        <v>6895984.412498554</v>
+        <v>6895867</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,74 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123211071</v>
+        <v>133653983</v>
       </c>
       <c r="B3" t="n">
-        <v>100257</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628380</v>
+        <v>628505</v>
       </c>
       <c r="R3" t="n">
-        <v>6896001</v>
+        <v>6895863</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,56 +851,50 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123182868</v>
+        <v>123198460</v>
       </c>
       <c r="B4" t="n">
-        <v>100257</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -943,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628512</v>
+        <v>628393</v>
       </c>
       <c r="R4" t="n">
-        <v>6895954</v>
+        <v>6895973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -978,7 +939,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +949,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,6 +973,876 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133654315</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>628391</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6895994</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123198544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628383</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6895980</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123198564</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628388</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6895967</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123182902</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628489</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6895940</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123198500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628384</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6895982</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>108922851</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628453</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896026</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123182868</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628512</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6895954</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123211071</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>628380</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6896001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19546-2026 artfynd.xlsx
+++ b/artfynd/A 19546-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133653949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133653983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133654315</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198544</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1406,6 +1441,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123182902</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198500</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108922851</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1733,6 +1783,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123182868</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,8 +1898,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123211071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>